--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{306D8565-DFDF-465D-BEB4-665EADBD747C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AD0152-BB47-405C-BBD2-6BF65567BE21}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{322E2C8B-C562-42B6-8575-F2D44E3C1606}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BDE146-65CD-4747-900E-1A3BE30EFAD1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D762AA8A-061D-4715-8DBF-85264D59581B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0276A8C0-8E2A-464B-83F6-66C71764133D}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AD0152-BB47-405C-BBD2-6BF65567BE21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A874E4-5EF5-4891-A5D0-DB00258D8B76}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BDE146-65CD-4747-900E-1A3BE30EFAD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4619AA2F-BBE5-4BEE-AEE0-285DDFDCDC09}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0276A8C0-8E2A-464B-83F6-66C71764133D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13EE2245-2B37-4C6C-8924-8C0ED8C47B03}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57A874E4-5EF5-4891-A5D0-DB00258D8B76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4956FDFC-3B85-4A72-9EC7-7521FA17C62C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4619AA2F-BBE5-4BEE-AEE0-285DDFDCDC09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66A3FE48-B218-488A-BD2E-D126EF89832A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13EE2245-2B37-4C6C-8924-8C0ED8C47B03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83BA07B2-721A-40BE-9F47-012ED40EF02C}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4956FDFC-3B85-4A72-9EC7-7521FA17C62C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33CB7BB6-3DC2-4A0D-9B0D-D9963950E655}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66A3FE48-B218-488A-BD2E-D126EF89832A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65BF2CF0-A410-4E4F-AAE3-A1D2A2B6A847}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83BA07B2-721A-40BE-9F47-012ED40EF02C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19D4AADC-F950-42DF-A870-E85C0779808E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -11,6 +11,632 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="207">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Tool_Use</t>
+  </si>
+  <si>
+    <t>Tool_Manufacture</t>
+  </si>
+  <si>
+    <t>True_Tool_Use</t>
+  </si>
+  <si>
+    <t>peak_workspace</t>
+  </si>
+  <si>
+    <t>relative_size</t>
+  </si>
+  <si>
+    <t>real_size</t>
+  </si>
+  <si>
+    <t>log10_mc1_mm</t>
+  </si>
+  <si>
+    <t>log10_pp1_mm</t>
+  </si>
+  <si>
+    <t>log10_dp1_mm</t>
+  </si>
+  <si>
+    <t>log10_mc2_mm</t>
+  </si>
+  <si>
+    <t>log10_pp2_mm</t>
+  </si>
+  <si>
+    <t>log10_ip2_mm</t>
+  </si>
+  <si>
+    <t>log10_dp2_mm</t>
+  </si>
+  <si>
+    <t>log10_mc3_mm</t>
+  </si>
+  <si>
+    <t>log10_pp3_mm</t>
+  </si>
+  <si>
+    <t>log10_ip3_mm</t>
+  </si>
+  <si>
+    <t>log10_dp3_mm</t>
+  </si>
+  <si>
+    <t>log10_mc4_mm</t>
+  </si>
+  <si>
+    <t>log10_pp4_mm</t>
+  </si>
+  <si>
+    <t>log10_ip4_mm</t>
+  </si>
+  <si>
+    <t>log10_dp4_mm</t>
+  </si>
+  <si>
+    <t>log10_mc5_mm</t>
+  </si>
+  <si>
+    <t>log10_pp5_mm</t>
+  </si>
+  <si>
+    <t>log10_ip5_mm</t>
+  </si>
+  <si>
+    <t>log10_dp5_mm</t>
+  </si>
+  <si>
+    <t>Adapis parisiensis</t>
+  </si>
+  <si>
+    <t>Afropithecus turkanensis</t>
+  </si>
+  <si>
+    <t>Allenopithecus nigroviridis</t>
+  </si>
+  <si>
+    <t>Alouatta belzebul</t>
+  </si>
+  <si>
+    <t>Alouatta caraya</t>
+  </si>
+  <si>
+    <t>Alouatta palliatus</t>
+  </si>
+  <si>
+    <t>Alouatta seniculus</t>
+  </si>
+  <si>
+    <t>Aotus azarae</t>
+  </si>
+  <si>
+    <t>Aotus trivirgatus</t>
+  </si>
+  <si>
+    <t>Archaeolemur edwardsi</t>
+  </si>
+  <si>
+    <t>Archaeolemur majori</t>
+  </si>
+  <si>
+    <t>Arctocebus calabarensis</t>
+  </si>
+  <si>
+    <t>Ardipithecus ramidus</t>
+  </si>
+  <si>
+    <t>Ateles belzebuth</t>
+  </si>
+  <si>
+    <t>Ateles fusciceps</t>
+  </si>
+  <si>
+    <t>Ateles geoffroyi</t>
+  </si>
+  <si>
+    <t>Ateles paniscus</t>
+  </si>
+  <si>
+    <t>Australopithecus afarensis</t>
+  </si>
+  <si>
+    <t>Australopithecus africanus</t>
+  </si>
+  <si>
+    <t>Australopithecus sediba</t>
+  </si>
+  <si>
+    <t>Avahi laniger</t>
+  </si>
+  <si>
+    <t>Brachyteles arachnoides</t>
+  </si>
+  <si>
+    <t>Plecturocebus donacophilus</t>
+  </si>
+  <si>
+    <t>Plecturocebus moloch</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Carpolestes simpsoni</t>
+  </si>
+  <si>
+    <t>Cebus albifrons</t>
+  </si>
+  <si>
+    <t>Cebus capucinus</t>
+  </si>
+  <si>
+    <t>Cebus olivaceus</t>
+  </si>
+  <si>
+    <t>Cercocebus agilis</t>
+  </si>
+  <si>
+    <t>Lophocebus aterrimus</t>
+  </si>
+  <si>
+    <t>Lophocebus albigena</t>
+  </si>
+  <si>
+    <t>Cercocebus atys</t>
+  </si>
+  <si>
+    <t>Cercocebus galeritus</t>
+  </si>
+  <si>
+    <t>Cercocebus torquatus</t>
+  </si>
+  <si>
+    <t>Chlorocebus aethiops</t>
+  </si>
+  <si>
+    <t>Cercopithecus albogularis</t>
+  </si>
+  <si>
+    <t>Cercopithecus ascanius</t>
+  </si>
+  <si>
+    <t>Cercopithecus campbelli</t>
+  </si>
+  <si>
+    <t>Cercopithecus cephus</t>
+  </si>
+  <si>
+    <t>Cercopithecus diana</t>
+  </si>
+  <si>
+    <t>Allochrocebus lhoesti</t>
+  </si>
+  <si>
+    <t>Cercopithecus mitis</t>
+  </si>
+  <si>
+    <t>Cercopithecus mona</t>
+  </si>
+  <si>
+    <t>Cercopithecus neglectus</t>
+  </si>
+  <si>
+    <t>Cercopithecus nictitans</t>
+  </si>
+  <si>
+    <t>Cheirogaleus major</t>
+  </si>
+  <si>
+    <t>Cheirogaleus medius</t>
+  </si>
+  <si>
+    <t>Chiropotes satanas</t>
+  </si>
+  <si>
+    <t>Colobus angolensis</t>
+  </si>
+  <si>
+    <t>Piliocolobus badius</t>
+  </si>
+  <si>
+    <t>Colobus guereza</t>
+  </si>
+  <si>
+    <t>Colobus polykomos</t>
+  </si>
+  <si>
+    <t>Darwinius masillae</t>
+  </si>
+  <si>
+    <t>Daubentonia madagascariensis</t>
+  </si>
+  <si>
+    <t>Dryomomys szalayi</t>
+  </si>
+  <si>
+    <t>Erythrocebus patas</t>
+  </si>
+  <si>
+    <t>Eulemur coronatus</t>
+  </si>
+  <si>
+    <t>Eulemur fulvus</t>
+  </si>
+  <si>
+    <t>Eulemur macaco</t>
+  </si>
+  <si>
+    <t>Eulemur mongoz</t>
+  </si>
+  <si>
+    <t>Eulemur rubriventer</t>
+  </si>
+  <si>
+    <t>Euoticus elegantulus</t>
+  </si>
+  <si>
+    <t>Europolemur klatti</t>
+  </si>
+  <si>
+    <t>Sciurocheirus alleni</t>
+  </si>
+  <si>
+    <t>Galagoides demidoff</t>
+  </si>
+  <si>
+    <t>Galago moholi</t>
+  </si>
+  <si>
+    <t>Galago senegalensis</t>
+  </si>
+  <si>
+    <t>Paragalago zanzibaricus</t>
+  </si>
+  <si>
+    <t>Gorilla beringei</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Hapalemur griseus</t>
+  </si>
+  <si>
+    <t>Prolemur simus</t>
+  </si>
+  <si>
+    <t>HispanopithecusHispanopithecus laietanus</t>
+  </si>
+  <si>
+    <t>Homo naledi</t>
+  </si>
+  <si>
+    <t>Homo neanderthalensis</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Hoolock hoolock</t>
+  </si>
+  <si>
+    <t>Hylobates agilis</t>
+  </si>
+  <si>
+    <t>Hylobates klossii</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Hylobates moloch</t>
+  </si>
+  <si>
+    <t>Hylobates muelleri</t>
+  </si>
+  <si>
+    <t>Hylobates pileatus</t>
+  </si>
+  <si>
+    <t>Indri indri</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>Lagothrix lagotricha</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Leontopithecus rosalia</t>
+  </si>
+  <si>
+    <t>Lepilemur leucopus</t>
+  </si>
+  <si>
+    <t>Lepilemur mustelinus</t>
+  </si>
+  <si>
+    <t>Lepilemur ruficaudatus</t>
+  </si>
+  <si>
+    <t>Leptadapis magnus</t>
+  </si>
+  <si>
+    <t>Loris tardigradus</t>
+  </si>
+  <si>
+    <t>Macaca arctoides</t>
+  </si>
+  <si>
+    <t>Macaca assamensis</t>
+  </si>
+  <si>
+    <t>Macaca fascicularis</t>
+  </si>
+  <si>
+    <t>Macaca fuscata</t>
+  </si>
+  <si>
+    <t>Macaca maura</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Macaca nemestrina</t>
+  </si>
+  <si>
+    <t>Macaca nigra</t>
+  </si>
+  <si>
+    <t>Macaca ochreata</t>
+  </si>
+  <si>
+    <t>Macaca silenus</t>
+  </si>
+  <si>
+    <t>Macaca sinica</t>
+  </si>
+  <si>
+    <t>Macaca sylvanus</t>
+  </si>
+  <si>
+    <t>Macaca thibetana</t>
+  </si>
+  <si>
+    <t>Macaca tonkeana</t>
+  </si>
+  <si>
+    <t>Mandrillus leucophaeus</t>
+  </si>
+  <si>
+    <t>Mandrillus sphinx</t>
+  </si>
+  <si>
+    <t>Mesopithecus pentelicus</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Microcolobus tugenensis</t>
+  </si>
+  <si>
+    <t>Miopithecus talapoin</t>
+  </si>
+  <si>
+    <t>Mirza coquereli</t>
+  </si>
+  <si>
+    <t>Nannodectes gidleyi</t>
+  </si>
+  <si>
+    <t>Nannodectes intermedius</t>
+  </si>
+  <si>
+    <t>Nasalis larvatus</t>
+  </si>
+  <si>
+    <t>Nomascus concolor</t>
+  </si>
+  <si>
+    <t>Notharctus tenebrosus</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Nycticebus pygmaeus</t>
+  </si>
+  <si>
+    <t>Oreopithecus bambolii</t>
+  </si>
+  <si>
+    <t>Otolemur crassicaudatus</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Pan paniscus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Papio cynocephalus</t>
+  </si>
+  <si>
+    <t>Papio hamadryas</t>
+  </si>
+  <si>
+    <t>Papio papio</t>
+  </si>
+  <si>
+    <t>Papio ursinus</t>
+  </si>
+  <si>
+    <t>Paranthropus boisei</t>
+  </si>
+  <si>
+    <t>Perodicticus potto</t>
+  </si>
+  <si>
+    <t>Phaner furcifer</t>
+  </si>
+  <si>
+    <t>Pierolapithecus catalaunicus</t>
+  </si>
+  <si>
+    <t>Piliocolobus kirkii</t>
+  </si>
+  <si>
+    <t>Piliocolobus rufomitratus</t>
+  </si>
+  <si>
+    <t>Pithecia monachus</t>
+  </si>
+  <si>
+    <t>Pithecia pithecia</t>
+  </si>
+  <si>
+    <t>Plesiadapis cookei</t>
+  </si>
+  <si>
+    <t>Plesiadapis insignis</t>
+  </si>
+  <si>
+    <t>Plesiadapis tricuspidens</t>
+  </si>
+  <si>
+    <t>Pongo sp.</t>
+  </si>
+  <si>
+    <t>Pongo abelii</t>
+  </si>
+  <si>
+    <t>Pongo pygmaeus</t>
+  </si>
+  <si>
+    <t>Presbytis comata</t>
+  </si>
+  <si>
+    <t>Trachypithecus cristatus</t>
+  </si>
+  <si>
+    <t>Presbytis frontata</t>
+  </si>
+  <si>
+    <t>Presbytis melalophos</t>
+  </si>
+  <si>
+    <t>Presbytis potenziani</t>
+  </si>
+  <si>
+    <t>Presbytis rubicunda</t>
+  </si>
+  <si>
+    <t>Presbytis thomasi</t>
+  </si>
+  <si>
+    <t>Procolobus verus</t>
+  </si>
+  <si>
+    <t>Ekembo heseloni</t>
+  </si>
+  <si>
+    <t>Propithecus diadema</t>
+  </si>
+  <si>
+    <t>Propithecus verreauxi</t>
+  </si>
+  <si>
+    <t>Ptilocercus lowii</t>
+  </si>
+  <si>
+    <t>Pygathrix nemaeus</t>
+  </si>
+  <si>
+    <t>Rhinopithecus roxellana</t>
+  </si>
+  <si>
+    <t>Saguinus midas</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Semnopithecus entellus</t>
+  </si>
+  <si>
+    <t>Semnopithecus johnii</t>
+  </si>
+  <si>
+    <t>Symphalangus syndactylus</t>
+  </si>
+  <si>
+    <t>Cephalopachus bancanus</t>
+  </si>
+  <si>
+    <t>Tarsius tarsier</t>
+  </si>
+  <si>
+    <t>Carlito syrichta</t>
+  </si>
+  <si>
+    <t>Teilhardina belgica</t>
+  </si>
+  <si>
+    <t>TheropithecusOmopithecus brumpti</t>
+  </si>
+  <si>
+    <t>Theropithecus gelada</t>
+  </si>
+  <si>
+    <t>Tinimomys graybulliensis</t>
+  </si>
+  <si>
+    <t>Trachypithecus auratus</t>
+  </si>
+  <si>
+    <t>Trachypithecus obscurus</t>
+  </si>
+  <si>
+    <t>Trachypithecus phayrei</t>
+  </si>
+  <si>
+    <t>Trachypithecus pileatus</t>
+  </si>
+  <si>
+    <t>Varecia variegata</t>
+  </si>
+  <si>
+    <t>Paralouatta varonai</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,153 +980,95 @@
   <dimension ref="A1:AA179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tool_Use</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tool_Manufacture</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>True_Tool_Use</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>peak_workspace</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>relative_size</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>real_size</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>log10_mc1_mm</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>log10_pp1_mm</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>log10_dp1_mm</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>log10_mc2_mm</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>log10_pp2_mm</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>log10_ip2_mm</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>log10_dp2_mm</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>log10_mc3_mm</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>log10_pp3_mm</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>log10_ip3_mm</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>log10_dp3_mm</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>log10_mc4_mm</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>log10_pp4_mm</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>log10_ip4_mm</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>log10_dp4_mm</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>log10_mc5_mm</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>log10_pp5_mm</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>log10_ip5_mm</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>log10_dp5_mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Adapis parisiensis</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Adapis parisiensis</t>
-        </is>
+    <row r="1" spans="1:27" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -530,16 +1098,12 @@
         <v>1.14519640611418</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Afropithecus turkanensis</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Afropithecus turkanensis</t>
-        </is>
+    <row r="3" spans="1:27">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -548,16 +1112,12 @@
         <v>1.45178643552429</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Allenopithecus nigroviridis</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Allenopithecus nigroviridis</t>
-        </is>
+    <row r="4" spans="1:27">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -572,16 +1132,12 @@
         <v>1.43328968519503</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Alouatta belzebul</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Alouatta belzebul</t>
-        </is>
+    <row r="5" spans="1:27">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -626,16 +1182,12 @@
         <v>1.44855173920158</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alouatta caraya</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Alouatta caraya</t>
-        </is>
+    <row r="6" spans="1:27">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -656,16 +1208,12 @@
         <v>1.48995847942483</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Alouatta palliatus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Alouatta palliatus</t>
-        </is>
+    <row r="7" spans="1:27">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -704,16 +1252,12 @@
         <v>1.44754562126701</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Alouatta seniculus</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Alouatta seniculus</t>
-        </is>
+    <row r="8" spans="1:27">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -776,16 +1320,12 @@
         <v>1.44983724551267</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Aotus azarae</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Aotus azarae</t>
-        </is>
+    <row r="9" spans="1:27">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -827,16 +1367,12 @@
         <v>1.14406801413637</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
+    <row r="10" spans="1:27">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -878,16 +1414,12 @@
         <v>1.10226355721697</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Archaeolemur edwardsi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Archaeolemur edwardsi</t>
-        </is>
+    <row r="11" spans="1:27">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -908,16 +1440,12 @@
         <v>1.55910828936663</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Archaeolemur majori</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Archaeolemur majori</t>
-        </is>
+    <row r="12" spans="1:27">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -932,16 +1460,12 @@
         <v>1.54468802230268</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Arctocebus calabarensis</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Arctocebus calabarensis</t>
-        </is>
+    <row r="13" spans="1:27">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -959,16 +1483,12 @@
         <v>0.868203455637116</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ardipithecus ramidus</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ardipithecus ramidus</t>
-        </is>
+    <row r="14" spans="1:27">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1001,16 +1521,12 @@
         <v>1.7427251313047</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ateles belzebuth</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ateles belzebuth</t>
-        </is>
+    <row r="15" spans="1:27">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1049,16 +1565,12 @@
         <v>1.67096907469322</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ateles fusciceps</t>
-        </is>
+    <row r="16" spans="1:27">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1079,16 +1591,12 @@
         <v>1.65417654187796</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
+    <row r="17" spans="1:26">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1133,16 +1641,12 @@
         <v>1.67117284271508</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ateles paniscus</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ateles paniscus</t>
-        </is>
+    <row r="18" spans="1:26">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1163,16 +1667,12 @@
         <v>1.69983772586725</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Australopithecus afarensis</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Australopithecus afarensis</t>
-        </is>
+    <row r="19" spans="1:26">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1223,16 +1723,12 @@
         <v>1.71180722904119</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Australopithecus africanus</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Australopithecus africanus</t>
-        </is>
+    <row r="20" spans="1:26">
+      <c r="A20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1250,16 +1746,12 @@
         <v>1.63748972951251</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Australopithecus sediba</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Australopithecus sediba</t>
-        </is>
+    <row r="21" spans="1:26">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1322,16 +1814,12 @@
         <v>1.22530928172586</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Avahi laniger</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Avahi laniger</t>
-        </is>
+    <row r="22" spans="1:26">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1358,16 +1846,12 @@
         <v>1.31829526793591</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Brachyteles arachnoides</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brachyteles arachnoides</t>
-        </is>
+    <row r="23" spans="1:26">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1388,16 +1872,12 @@
         <v>1.71474876072506</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Plecturocebus donacophilus</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Plecturocebus donacophilus</t>
-        </is>
+    <row r="24" spans="1:26">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1415,16 +1895,12 @@
         <v>1.09342168516224</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Plecturocebus moloch</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Plecturocebus moloch</t>
-        </is>
+    <row r="25" spans="1:26">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1439,16 +1915,12 @@
         <v>1.02118929906994</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
+    <row r="26" spans="1:26">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1490,16 +1962,12 @@
         <v>0.965828909342021</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Carpolestes simpsoni</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Carpolestes simpsoni</t>
-        </is>
+    <row r="27" spans="1:26">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1517,16 +1985,12 @@
         <v>0.361727836017593</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Cebus albifrons</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cebus albifrons</t>
-        </is>
+    <row r="28" spans="1:26">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1589,16 +2053,12 @@
         <v>1.32844029389074</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cebus capucinus</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cebus capucinus</t>
-        </is>
+    <row r="29" spans="1:26">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1625,16 +2085,12 @@
         <v>1.36097188372594</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Cebus olivaceus</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cebus olivaceus</t>
-        </is>
+    <row r="30" spans="1:26">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1682,16 +2138,12 @@
         <v>1.32193071474978</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Cercocebus agilis</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Cercocebus agilis</t>
-        </is>
+    <row r="31" spans="1:26">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>56</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1718,16 +2170,12 @@
         <v>1.55878854373695</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Lophocebus aterrimus</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Lophocebus aterrimus</t>
-        </is>
+    <row r="32" spans="1:26">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" t="s">
+        <v>57</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1754,16 +2202,12 @@
         <v>1.58804749698608</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Lophocebus albigena</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Lophocebus albigena</t>
-        </is>
+    <row r="33" spans="1:24">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" t="s">
+        <v>58</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1790,16 +2234,12 @@
         <v>1.56295866865462</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Cercocebus atys</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Cercocebus atys</t>
-        </is>
+    <row r="34" spans="1:24">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" t="s">
+        <v>59</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1823,16 +2263,12 @@
         <v>1.54629583512144</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cercocebus galeritus</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Cercocebus galeritus</t>
-        </is>
+    <row r="35" spans="1:24">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>60</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1853,16 +2289,12 @@
         <v>1.44622640177816</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Cercocebus torquatus</t>
-        </is>
+    <row r="36" spans="1:24">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1889,16 +2321,12 @@
         <v>1.60124492481052</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Chlorocebus aethiops</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Chlorocebus aethiops</t>
-        </is>
+    <row r="37" spans="1:24">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s">
+        <v>62</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1931,16 +2359,12 @@
         <v>1.42406452541749</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Cercopithecus albogularis</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Cercopithecus albogularis</t>
-        </is>
+    <row r="38" spans="1:24">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s">
+        <v>63</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1961,16 +2385,12 @@
         <v>1.41455555622922</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
+    <row r="39" spans="1:24">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2018,16 +2438,12 @@
         <v>1.37403500765351</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Cercopithecus campbelli</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cercopithecus campbelli</t>
-        </is>
+    <row r="40" spans="1:24">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" t="s">
+        <v>65</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2048,16 +2464,12 @@
         <v>1.3451776165427</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Cercopithecus cephus</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Cercopithecus cephus</t>
-        </is>
+    <row r="41" spans="1:24">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" t="s">
+        <v>66</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2072,16 +2484,12 @@
         <v>1.44232295574557</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Cercopithecus diana</t>
-        </is>
+    <row r="42" spans="1:24">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2096,16 +2504,12 @@
         <v>1.45408227073109</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Allochrocebus lhoesti</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Allochrocebus lhoesti</t>
-        </is>
+    <row r="43" spans="1:24">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>68</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2120,16 +2524,12 @@
         <v>1.52348633234323</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Cercopithecus mitis</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Cercopithecus mitis</t>
-        </is>
+    <row r="44" spans="1:24">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>69</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2171,16 +2571,12 @@
         <v>1.41559910869476</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Cercopithecus mona</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Cercopithecus mona</t>
-        </is>
+    <row r="45" spans="1:24">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>70</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2195,16 +2591,12 @@
         <v>1.40739090447073</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cercopithecus neglectus</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Cercopithecus neglectus</t>
-        </is>
+    <row r="46" spans="1:24">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" t="s">
+        <v>71</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2225,16 +2617,12 @@
         <v>1.44090908206522</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cercopithecus nictitans</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Cercopithecus nictitans</t>
-        </is>
+    <row r="47" spans="1:24">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" t="s">
+        <v>72</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2249,16 +2637,12 @@
         <v>1.47668674294564</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Cheirogaleus major</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Cheirogaleus major</t>
-        </is>
+    <row r="48" spans="1:24">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" t="s">
+        <v>73</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2285,16 +2669,12 @@
         <v>0.939685617103282</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Cheirogaleus medius</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Cheirogaleus medius</t>
-        </is>
+    <row r="49" spans="1:27">
+      <c r="A49" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" t="s">
+        <v>74</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2321,16 +2701,12 @@
         <v>0.757016234731301</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Chiropotes satanas</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Chiropotes satanas</t>
-        </is>
+    <row r="50" spans="1:27">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" t="s">
+        <v>75</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2351,16 +2727,12 @@
         <v>1.339782584656</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Colobus angolensis</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Colobus angolensis</t>
-        </is>
+    <row r="51" spans="1:27">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
+        <v>76</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2402,16 +2774,12 @@
         <v>1.60122703798179</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Piliocolobus badius</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Piliocolobus badius</t>
-        </is>
+    <row r="52" spans="1:27">
+      <c r="A52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" t="s">
+        <v>77</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2456,16 +2824,12 @@
         <v>1.51668838134178</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Colobus guereza</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Colobus guereza</t>
-        </is>
+    <row r="53" spans="1:27">
+      <c r="A53" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2507,16 +2871,12 @@
         <v>1.59050746200858</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Colobus polykomos</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Colobus polykomos</t>
-        </is>
+    <row r="54" spans="1:27">
+      <c r="A54" t="s">
+        <v>79</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2543,16 +2903,12 @@
         <v>1.60791052538138</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Darwinius masillae</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Darwinius masillae</t>
-        </is>
+    <row r="55" spans="1:27">
+      <c r="A55" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" t="s">
+        <v>80</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2612,16 +2968,12 @@
         <v>0.495544337546448</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascariensis</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascariensis</t>
-        </is>
+    <row r="56" spans="1:27">
+      <c r="A56" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" t="s">
+        <v>81</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2648,16 +3000,12 @@
         <v>1.32301993299933</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Dryomomys szalayi</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Dryomomys szalayi</t>
-        </is>
+    <row r="57" spans="1:27">
+      <c r="A57" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" t="s">
+        <v>82</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2666,16 +3014,12 @@
         <v>0.621176281775035</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Erythrocebus patas</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Erythrocebus patas</t>
-        </is>
+    <row r="58" spans="1:27">
+      <c r="A58" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" t="s">
+        <v>83</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2723,16 +3067,12 @@
         <v>1.51066019147352</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Eulemur coronatus</t>
-        </is>
+    <row r="59" spans="1:27">
+      <c r="A59" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" t="s">
+        <v>84</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2747,16 +3087,12 @@
         <v>1.02530586526477</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Eulemur fulvus</t>
-        </is>
+    <row r="60" spans="1:27">
+      <c r="A60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2789,16 +3125,12 @@
         <v>1.28216877830464</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Eulemur macaco</t>
-        </is>
+    <row r="61" spans="1:27">
+      <c r="A61" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" t="s">
+        <v>86</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2825,16 +3157,12 @@
         <v>1.30285021270231</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Eulemur mongoz</t>
-        </is>
+    <row r="62" spans="1:27">
+      <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" t="s">
+        <v>87</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2861,16 +3189,12 @@
         <v>1.23975814551305</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Eulemur rubriventer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Eulemur rubriventer</t>
-        </is>
+    <row r="63" spans="1:27">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2885,16 +3209,12 @@
         <v>1.10720996964787</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Euoticus elegantulus</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Euoticus elegantulus</t>
-        </is>
+    <row r="64" spans="1:27">
+      <c r="A64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" t="s">
+        <v>89</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2921,16 +3241,12 @@
         <v>0.996730515435153</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Europolemur klatti</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Europolemur klatti</t>
-        </is>
+    <row r="65" spans="1:27">
+      <c r="A65" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2987,16 +3303,12 @@
         <v>1.02571538390134</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Sciurocheirus alleni</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Sciurocheirus alleni</t>
-        </is>
+    <row r="66" spans="1:27">
+      <c r="A66" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" t="s">
+        <v>91</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3014,16 +3326,12 @@
         <v>0.932811868611632</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
+    <row r="67" spans="1:27">
+      <c r="A67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s">
+        <v>92</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3050,16 +3358,12 @@
         <v>0.6878632481960421</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Galago moholi</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Galago moholi</t>
-        </is>
+    <row r="68" spans="1:27">
+      <c r="A68" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" t="s">
+        <v>93</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3086,16 +3390,12 @@
         <v>0.798880735242388</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
+    <row r="69" spans="1:27">
+      <c r="A69" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" t="s">
+        <v>94</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3128,16 +3428,12 @@
         <v>0.818005830532529</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Paragalago zanzibaricus</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Paragalago zanzibaricus</t>
-        </is>
+    <row r="70" spans="1:27">
+      <c r="A70" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" t="s">
+        <v>95</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3152,16 +3448,12 @@
         <v>0.7944880466591701</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Gorilla beringei</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Gorilla beringei</t>
-        </is>
+    <row r="71" spans="1:27">
+      <c r="A71" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" t="s">
+        <v>96</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3194,16 +3486,12 @@
         <v>1.89756016128198</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+    <row r="72" spans="1:27">
+      <c r="A72" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" t="s">
+        <v>97</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3263,16 +3551,12 @@
         <v>1.93231166321417</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Hapalemur griseus</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Hapalemur griseus</t>
-        </is>
+    <row r="73" spans="1:27">
+      <c r="A73" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3299,16 +3583,12 @@
         <v>1.17035951845401</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Prolemur simus</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Prolemur simus</t>
-        </is>
+    <row r="74" spans="1:27">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" t="s">
+        <v>99</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3323,16 +3603,12 @@
         <v>1.06818586174616</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>HispanopithecusHispanopithecus laietanus</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>HispanopithecusHispanopithecus laietanus</t>
-        </is>
+    <row r="75" spans="1:27">
+      <c r="A75" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" t="s">
+        <v>100</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3353,16 +3629,12 @@
         <v>1.6159500516564</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Homo naledi</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Homo naledi</t>
-        </is>
+    <row r="76" spans="1:27">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" t="s">
+        <v>101</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3425,16 +3697,12 @@
         <v>1.09342168516224</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Homo neanderthalensis</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Homo neanderthalensis</t>
-        </is>
+    <row r="77" spans="1:27">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" t="s">
+        <v>102</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3491,16 +3759,12 @@
         <v>1.71767050300226</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+    <row r="78" spans="1:27">
+      <c r="A78" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" t="s">
+        <v>103</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3560,16 +3824,12 @@
         <v>1.72706203877614</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Hoolock hoolock</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Hoolock hoolock</t>
-        </is>
+    <row r="79" spans="1:27">
+      <c r="A79" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79" t="s">
+        <v>104</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -3596,16 +3856,12 @@
         <v>1.66138669778177</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Hylobates agilis</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Hylobates agilis</t>
-        </is>
+    <row r="80" spans="1:27">
+      <c r="A80" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80" t="s">
+        <v>105</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3638,16 +3894,12 @@
         <v>1.68584917961594</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Hylobates klossii</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Hylobates klossii</t>
-        </is>
+    <row r="81" spans="1:25">
+      <c r="A81" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" t="s">
+        <v>106</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3668,16 +3920,12 @@
         <v>1.60726196053894</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
+    <row r="82" spans="1:25">
+      <c r="A82" t="s">
+        <v>107</v>
+      </c>
+      <c r="B82" t="s">
+        <v>107</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -3740,16 +3988,12 @@
         <v>1.6969646324301</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Hylobates moloch</t>
-        </is>
+    <row r="83" spans="1:25">
+      <c r="A83" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" t="s">
+        <v>108</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3773,16 +4017,12 @@
         <v>1.46389298898591</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Hylobates muelleri</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Hylobates muelleri</t>
-        </is>
+    <row r="84" spans="1:25">
+      <c r="A84" t="s">
+        <v>109</v>
+      </c>
+      <c r="B84" t="s">
+        <v>109</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3815,16 +4055,12 @@
         <v>1.66167073604036</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Hylobates pileatus</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Hylobates pileatus</t>
-        </is>
+    <row r="85" spans="1:25">
+      <c r="A85" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85" t="s">
+        <v>110</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3848,16 +4084,12 @@
         <v>1.46982201597816</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Indri indri</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Indri indri</t>
-        </is>
+    <row r="86" spans="1:25">
+      <c r="A86" t="s">
+        <v>111</v>
+      </c>
+      <c r="B86" t="s">
+        <v>111</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3884,16 +4116,12 @@
         <v>1.71076592368989</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Lagothrix lagotricha</t>
-        </is>
+    <row r="87" spans="1:25">
+      <c r="A87" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" t="s">
+        <v>113</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3920,16 +4148,12 @@
         <v>1.48429983934679</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+    <row r="88" spans="1:25">
+      <c r="A88" t="s">
+        <v>114</v>
+      </c>
+      <c r="B88" t="s">
+        <v>114</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -3962,16 +4186,12 @@
         <v>1.2724604801459</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Leontopithecus rosalia</t>
-        </is>
+    <row r="89" spans="1:25">
+      <c r="A89" t="s">
+        <v>115</v>
+      </c>
+      <c r="B89" t="s">
+        <v>115</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3992,16 +4212,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Lepilemur leucopus</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Lepilemur leucopus</t>
-        </is>
+    <row r="90" spans="1:25">
+      <c r="A90" t="s">
+        <v>116</v>
+      </c>
+      <c r="B90" t="s">
+        <v>116</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4028,16 +4244,12 @@
         <v>1.08451669984494</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Lepilemur mustelinus</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Lepilemur mustelinus</t>
-        </is>
+    <row r="91" spans="1:25">
+      <c r="A91" t="s">
+        <v>117</v>
+      </c>
+      <c r="B91" t="s">
+        <v>117</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4052,16 +4264,12 @@
         <v>0.999130541287371</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
+    <row r="92" spans="1:25">
+      <c r="A92" t="s">
+        <v>118</v>
+      </c>
+      <c r="B92" t="s">
+        <v>118</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4076,16 +4284,12 @@
         <v>0.887054378050957</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Leptadapis magnus</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Leptadapis magnus</t>
-        </is>
+    <row r="93" spans="1:25">
+      <c r="A93" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" t="s">
+        <v>119</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4112,16 +4316,12 @@
         <v>1.42045085910607</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Loris tardigradus</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Loris tardigradus</t>
-        </is>
+    <row r="94" spans="1:25">
+      <c r="A94" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" t="s">
+        <v>120</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4148,16 +4348,12 @@
         <v>0.807341707575163</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Macaca arctoides</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Macaca arctoides</t>
-        </is>
+    <row r="95" spans="1:25">
+      <c r="A95" t="s">
+        <v>121</v>
+      </c>
+      <c r="B95" t="s">
+        <v>121</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -4172,16 +4368,12 @@
         <v>1.47538059314336</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Macaca assamensis</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Macaca assamensis</t>
-        </is>
+    <row r="96" spans="1:25">
+      <c r="A96" t="s">
+        <v>122</v>
+      </c>
+      <c r="B96" t="s">
+        <v>122</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4196,16 +4388,12 @@
         <v>1.51982799377572</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Macaca fascicularis</t>
-        </is>
+    <row r="97" spans="1:24">
+      <c r="A97" t="s">
+        <v>123</v>
+      </c>
+      <c r="B97" t="s">
+        <v>123</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -4268,16 +4456,12 @@
         <v>1.39317728332193</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Macaca fuscata</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Macaca fuscata</t>
-        </is>
+    <row r="98" spans="1:24">
+      <c r="A98" t="s">
+        <v>124</v>
+      </c>
+      <c r="B98" t="s">
+        <v>124</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -4313,16 +4497,12 @@
         <v>1.21879799811174</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Macaca maura</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Macaca maura</t>
-        </is>
+    <row r="99" spans="1:24">
+      <c r="A99" t="s">
+        <v>125</v>
+      </c>
+      <c r="B99" t="s">
+        <v>125</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4361,16 +4541,12 @@
         <v>1.58489634413745</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
+    <row r="100" spans="1:24">
+      <c r="A100" t="s">
+        <v>126</v>
+      </c>
+      <c r="B100" t="s">
+        <v>126</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -4433,16 +4609,12 @@
         <v>1.52128937079521</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
+    <row r="101" spans="1:24">
+      <c r="A101" t="s">
+        <v>127</v>
+      </c>
+      <c r="B101" t="s">
+        <v>127</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4487,16 +4659,12 @@
         <v>1.5887757562041</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Macaca nigra</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Macaca nigra</t>
-        </is>
+    <row r="102" spans="1:24">
+      <c r="A102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" t="s">
+        <v>128</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -4541,16 +4709,12 @@
         <v>1.58927922123597</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Macaca ochreata</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Macaca ochreata</t>
-        </is>
+    <row r="103" spans="1:24">
+      <c r="A103" t="s">
+        <v>129</v>
+      </c>
+      <c r="B103" t="s">
+        <v>129</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4562,16 +4726,12 @@
         <v>1.56264967221192</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Macaca silenus</t>
-        </is>
+    <row r="104" spans="1:24">
+      <c r="A104" t="s">
+        <v>130</v>
+      </c>
+      <c r="B104" t="s">
+        <v>130</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4601,16 +4761,12 @@
         <v>1.26481782300954</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Macaca sinica</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Macaca sinica</t>
-        </is>
+    <row r="105" spans="1:24">
+      <c r="A105" t="s">
+        <v>131</v>
+      </c>
+      <c r="B105" t="s">
+        <v>131</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4634,16 +4790,12 @@
         <v>1.22788670461367</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Macaca sylvanus</t>
-        </is>
+    <row r="106" spans="1:24">
+      <c r="A106" t="s">
+        <v>132</v>
+      </c>
+      <c r="B106" t="s">
+        <v>132</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4673,16 +4825,12 @@
         <v>1.31104711642151</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Macaca thibetana</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Macaca thibetana</t>
-        </is>
+    <row r="107" spans="1:24">
+      <c r="A107" t="s">
+        <v>133</v>
+      </c>
+      <c r="B107" t="s">
+        <v>133</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4703,16 +4851,12 @@
         <v>1.55071742346928</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Macaca tonkeana</t>
-        </is>
+    <row r="108" spans="1:24">
+      <c r="A108" t="s">
+        <v>134</v>
+      </c>
+      <c r="B108" t="s">
+        <v>134</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4730,16 +4874,12 @@
         <v>1.60195140413352</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Mandrillus leucophaeus</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Mandrillus leucophaeus</t>
-        </is>
+    <row r="109" spans="1:24">
+      <c r="A109" t="s">
+        <v>135</v>
+      </c>
+      <c r="B109" t="s">
+        <v>135</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -4784,16 +4924,12 @@
         <v>1.7260476681558</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Mandrillus sphinx</t>
-        </is>
+    <row r="110" spans="1:24">
+      <c r="A110" t="s">
+        <v>136</v>
+      </c>
+      <c r="B110" t="s">
+        <v>136</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -4838,16 +4974,12 @@
         <v>1.7257037861643</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Mesopithecus pentelicus</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Mesopithecus pentelicus</t>
-        </is>
+    <row r="111" spans="1:24">
+      <c r="A111" t="s">
+        <v>137</v>
+      </c>
+      <c r="B111" t="s">
+        <v>137</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4868,16 +5000,12 @@
         <v>1.43695733066945</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
+    <row r="112" spans="1:24">
+      <c r="A112" t="s">
+        <v>138</v>
+      </c>
+      <c r="B112" t="s">
+        <v>138</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -4904,16 +5032,12 @@
         <v>0.619946654847815</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Microcolobus tugenensis</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Microcolobus tugenensis</t>
-        </is>
+    <row r="113" spans="1:27">
+      <c r="A113" t="s">
+        <v>139</v>
+      </c>
+      <c r="B113" t="s">
+        <v>139</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4922,16 +5046,12 @@
         <v>1.48287358360875</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
+    <row r="114" spans="1:27">
+      <c r="A114" t="s">
+        <v>140</v>
+      </c>
+      <c r="B114" t="s">
+        <v>140</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4955,16 +5075,12 @@
         <v>1.20803804935318</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Mirza coquereli</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Mirza coquereli</t>
-        </is>
+    <row r="115" spans="1:27">
+      <c r="A115" t="s">
+        <v>141</v>
+      </c>
+      <c r="B115" t="s">
+        <v>141</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -4979,16 +5095,12 @@
         <v>0.75966784468963</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Nannodectes gidleyi</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Nannodectes gidleyi</t>
-        </is>
+    <row r="116" spans="1:27">
+      <c r="A116" t="s">
+        <v>142</v>
+      </c>
+      <c r="B116" t="s">
+        <v>142</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5000,16 +5112,12 @@
         <v>1.07990446766672</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Nannodectes intermedius</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Nannodectes intermedius</t>
-        </is>
+    <row r="117" spans="1:27">
+      <c r="A117" t="s">
+        <v>143</v>
+      </c>
+      <c r="B117" t="s">
+        <v>143</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -5033,16 +5141,12 @@
         <v>0.939519252618618</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Nasalis larvatus</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Nasalis larvatus</t>
-        </is>
+    <row r="118" spans="1:27">
+      <c r="A118" t="s">
+        <v>144</v>
+      </c>
+      <c r="B118" t="s">
+        <v>144</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -5081,16 +5185,12 @@
         <v>1.67369935497777</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Nomascus concolor</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Nomascus concolor</t>
-        </is>
+    <row r="119" spans="1:27">
+      <c r="A119" t="s">
+        <v>145</v>
+      </c>
+      <c r="B119" t="s">
+        <v>145</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5111,16 +5211,12 @@
         <v>1.70225816316209</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Notharctus tenebrosus</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Notharctus tenebrosus</t>
-        </is>
+    <row r="120" spans="1:27">
+      <c r="A120" t="s">
+        <v>146</v>
+      </c>
+      <c r="B120" t="s">
+        <v>146</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -5177,16 +5273,12 @@
         <v>0.952308009662125</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
+    <row r="121" spans="1:27">
+      <c r="A121" t="s">
+        <v>147</v>
+      </c>
+      <c r="B121" t="s">
+        <v>147</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5213,16 +5305,12 @@
         <v>1.02448566769917</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Nycticebus pygmaeus</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Nycticebus pygmaeus</t>
-        </is>
+    <row r="122" spans="1:27">
+      <c r="A122" t="s">
+        <v>148</v>
+      </c>
+      <c r="B122" t="s">
+        <v>148</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -5237,16 +5325,12 @@
         <v>0.830588668685144</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Oreopithecus bambolii</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Oreopithecus bambolii</t>
-        </is>
+    <row r="123" spans="1:27">
+      <c r="A123" t="s">
+        <v>149</v>
+      </c>
+      <c r="B123" t="s">
+        <v>149</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -5273,16 +5357,12 @@
         <v>1.4945719842302</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Otolemur crassicaudatus</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Otolemur crassicaudatus</t>
-        </is>
+    <row r="124" spans="1:27">
+      <c r="A124" t="s">
+        <v>150</v>
+      </c>
+      <c r="B124" t="s">
+        <v>150</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -5309,16 +5389,12 @@
         <v>1.08386080086657</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
+    <row r="125" spans="1:27">
+      <c r="A125" t="s">
+        <v>151</v>
+      </c>
+      <c r="B125" t="s">
+        <v>151</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -5345,16 +5421,12 @@
         <v>1.07353506505878</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Pan paniscus</t>
-        </is>
+    <row r="126" spans="1:27">
+      <c r="A126" t="s">
+        <v>152</v>
+      </c>
+      <c r="B126" t="s">
+        <v>152</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -5414,16 +5486,12 @@
         <v>1.84605862896419</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="127" spans="1:27">
+      <c r="A127" t="s">
+        <v>153</v>
+      </c>
+      <c r="B127" t="s">
+        <v>153</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -5486,16 +5554,12 @@
         <v>1.86835049964797</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
+    <row r="128" spans="1:27">
+      <c r="A128" t="s">
+        <v>154</v>
+      </c>
+      <c r="B128" t="s">
+        <v>154</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -5528,16 +5592,12 @@
         <v>1.71049211646599</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Papio cynocephalus</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Papio cynocephalus</t>
-        </is>
+    <row r="129" spans="1:25">
+      <c r="A129" t="s">
+        <v>155</v>
+      </c>
+      <c r="B129" t="s">
+        <v>155</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -5573,16 +5633,12 @@
         <v>1.73739144997848</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Papio hamadryas</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Papio hamadryas</t>
-        </is>
+    <row r="130" spans="1:25">
+      <c r="A130" t="s">
+        <v>156</v>
+      </c>
+      <c r="B130" t="s">
+        <v>156</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -5645,16 +5701,12 @@
         <v>1.69162605324364</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Papio papio</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Papio papio</t>
-        </is>
+    <row r="131" spans="1:25">
+      <c r="A131" t="s">
+        <v>157</v>
+      </c>
+      <c r="B131" t="s">
+        <v>157</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5687,16 +5739,12 @@
         <v>1.67778939106886</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Papio ursinus</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Papio ursinus</t>
-        </is>
+    <row r="132" spans="1:25">
+      <c r="A132" t="s">
+        <v>158</v>
+      </c>
+      <c r="B132" t="s">
+        <v>158</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -5717,16 +5765,12 @@
         <v>1.67440181284528</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Paranthropus boisei</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Paranthropus boisei</t>
-        </is>
+    <row r="133" spans="1:25">
+      <c r="A133" t="s">
+        <v>159</v>
+      </c>
+      <c r="B133" t="s">
+        <v>159</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -5750,16 +5794,12 @@
         <v>1.52504480703685</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
+    <row r="134" spans="1:25">
+      <c r="A134" t="s">
+        <v>160</v>
+      </c>
+      <c r="B134" t="s">
+        <v>160</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -5777,16 +5817,12 @@
         <v>1.11360915107303</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Phaner furcifer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Phaner furcifer</t>
-        </is>
+    <row r="135" spans="1:25">
+      <c r="A135" t="s">
+        <v>161</v>
+      </c>
+      <c r="B135" t="s">
+        <v>161</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -5801,16 +5837,12 @@
         <v>0.82020145948564</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Pierolapithecus catalaunicus</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Pierolapithecus catalaunicus</t>
-        </is>
+    <row r="136" spans="1:25">
+      <c r="A136" t="s">
+        <v>162</v>
+      </c>
+      <c r="B136" t="s">
+        <v>162</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5819,16 +5851,12 @@
         <v>1.27415784926368</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Piliocolobus kirkii</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Piliocolobus kirkii</t>
-        </is>
+    <row r="137" spans="1:25">
+      <c r="A137" t="s">
+        <v>163</v>
+      </c>
+      <c r="B137" t="s">
+        <v>163</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -5849,16 +5877,12 @@
         <v>1.54282542695918</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Piliocolobus rufomitratus</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Piliocolobus rufomitratus</t>
-        </is>
+    <row r="138" spans="1:25">
+      <c r="A138" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" t="s">
+        <v>164</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5879,16 +5903,12 @@
         <v>1.58035466110659</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Pithecia monachus</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Pithecia monachus</t>
-        </is>
+    <row r="139" spans="1:25">
+      <c r="A139" t="s">
+        <v>165</v>
+      </c>
+      <c r="B139" t="s">
+        <v>165</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -5930,16 +5950,12 @@
         <v>1.27626729251348</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Pithecia pithecia</t>
-        </is>
+    <row r="140" spans="1:25">
+      <c r="A140" t="s">
+        <v>166</v>
+      </c>
+      <c r="B140" t="s">
+        <v>166</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5981,16 +5997,12 @@
         <v>1.28916420108846</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Plesiadapis cookei</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Plesiadapis cookei</t>
-        </is>
+    <row r="141" spans="1:25">
+      <c r="A141" t="s">
+        <v>167</v>
+      </c>
+      <c r="B141" t="s">
+        <v>167</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5999,16 +6011,12 @@
         <v>1.05690485133647</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Plesiadapis insignis</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Plesiadapis insignis</t>
-        </is>
+    <row r="142" spans="1:25">
+      <c r="A142" t="s">
+        <v>168</v>
+      </c>
+      <c r="B142" t="s">
+        <v>168</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -6023,16 +6031,12 @@
         <v>0.89209460269048</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Plesiadapis tricuspidens</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Plesiadapis tricuspidens</t>
-        </is>
+    <row r="143" spans="1:25">
+      <c r="A143" t="s">
+        <v>169</v>
+      </c>
+      <c r="B143" t="s">
+        <v>169</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -6047,16 +6051,12 @@
         <v>1.15986784709257</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Pongo sp.</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Pongo abelii</t>
-        </is>
+    <row r="144" spans="1:25">
+      <c r="A144" t="s">
+        <v>170</v>
+      </c>
+      <c r="B144" t="s">
+        <v>171</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -6095,16 +6095,12 @@
         <v>1.92766543928285</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
+    <row r="145" spans="1:24">
+      <c r="A145" t="s">
+        <v>172</v>
+      </c>
+      <c r="B145" t="s">
+        <v>172</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -6167,16 +6163,12 @@
         <v>1.93145787068901</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Presbytis comata</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Presbytis comata</t>
-        </is>
+    <row r="146" spans="1:24">
+      <c r="A146" t="s">
+        <v>173</v>
+      </c>
+      <c r="B146" t="s">
+        <v>173</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -6197,16 +6189,12 @@
         <v>1.5792117802315</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Trachypithecus cristatus</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Trachypithecus cristatus</t>
-        </is>
+    <row r="147" spans="1:24">
+      <c r="A147" t="s">
+        <v>174</v>
+      </c>
+      <c r="B147" t="s">
+        <v>174</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -6269,16 +6257,12 @@
         <v>1.53375913489462</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Presbytis frontata</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Presbytis frontata</t>
-        </is>
+    <row r="148" spans="1:24">
+      <c r="A148" t="s">
+        <v>175</v>
+      </c>
+      <c r="B148" t="s">
+        <v>175</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -6290,16 +6274,12 @@
         <v>1.58726184969253</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Presbytis melalophos</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Presbytis melalophos</t>
-        </is>
+    <row r="149" spans="1:24">
+      <c r="A149" t="s">
+        <v>176</v>
+      </c>
+      <c r="B149" t="s">
+        <v>176</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -6320,16 +6300,12 @@
         <v>1.59439255037543</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Presbytis potenziani</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Presbytis potenziani</t>
-        </is>
+    <row r="150" spans="1:24">
+      <c r="A150" t="s">
+        <v>177</v>
+      </c>
+      <c r="B150" t="s">
+        <v>177</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -6341,16 +6317,12 @@
         <v>1.57472558359407</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Presbytis rubicunda</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Presbytis rubicunda</t>
-        </is>
+    <row r="151" spans="1:24">
+      <c r="A151" t="s">
+        <v>178</v>
+      </c>
+      <c r="B151" t="s">
+        <v>178</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6371,16 +6343,12 @@
         <v>1.58877202465496</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Presbytis thomasi</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Presbytis thomasi</t>
-        </is>
+    <row r="152" spans="1:24">
+      <c r="A152" t="s">
+        <v>179</v>
+      </c>
+      <c r="B152" t="s">
+        <v>179</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6392,16 +6360,12 @@
         <v>1.59791447120253</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Procolobus verus</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Procolobus verus</t>
-        </is>
+    <row r="153" spans="1:24">
+      <c r="A153" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" t="s">
+        <v>180</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -6413,16 +6377,12 @@
         <v>1.49387611085282</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Ekembo heseloni</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Ekembo heseloni</t>
-        </is>
+    <row r="154" spans="1:24">
+      <c r="A154" t="s">
+        <v>181</v>
+      </c>
+      <c r="B154" t="s">
+        <v>181</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6449,16 +6409,12 @@
         <v>1.23044892137827</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Propithecus diadema</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Propithecus diadema</t>
-        </is>
+    <row r="155" spans="1:24">
+      <c r="A155" t="s">
+        <v>182</v>
+      </c>
+      <c r="B155" t="s">
+        <v>182</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6485,16 +6441,12 @@
         <v>1.6031660326527</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
+    <row r="156" spans="1:24">
+      <c r="A156" t="s">
+        <v>183</v>
+      </c>
+      <c r="B156" t="s">
+        <v>183</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6521,16 +6473,12 @@
         <v>1.43870053290074</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Ptilocercus lowii</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Ptilocercus lowii</t>
-        </is>
+    <row r="157" spans="1:24">
+      <c r="A157" t="s">
+        <v>184</v>
+      </c>
+      <c r="B157" t="s">
+        <v>184</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -6551,16 +6499,12 @@
         <v>0.606202163753863</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Pygathrix nemaeus</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Pygathrix nemaeus</t>
-        </is>
+    <row r="158" spans="1:24">
+      <c r="A158" t="s">
+        <v>185</v>
+      </c>
+      <c r="B158" t="s">
+        <v>185</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6572,16 +6516,12 @@
         <v>1.68087917442681</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Rhinopithecus roxellana</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Rhinopithecus roxellana</t>
-        </is>
+    <row r="159" spans="1:24">
+      <c r="A159" t="s">
+        <v>186</v>
+      </c>
+      <c r="B159" t="s">
+        <v>186</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -6602,16 +6542,12 @@
         <v>1.59769518592551</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
+    <row r="160" spans="1:24">
+      <c r="A160" t="s">
+        <v>187</v>
+      </c>
+      <c r="B160" t="s">
+        <v>187</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -6626,16 +6562,12 @@
         <v>0.849419413796899</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
+    <row r="161" spans="1:27">
+      <c r="A161" t="s">
+        <v>188</v>
+      </c>
+      <c r="B161" t="s">
+        <v>188</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -6656,16 +6588,12 @@
         <v>0.841984804590114</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="162" spans="1:27">
+      <c r="A162" t="s">
+        <v>189</v>
+      </c>
+      <c r="B162" t="s">
+        <v>189</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -6707,16 +6635,12 @@
         <v>1.09208907867528</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
+    <row r="163" spans="1:27">
+      <c r="A163" t="s">
+        <v>190</v>
+      </c>
+      <c r="B163" t="s">
+        <v>190</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6779,16 +6703,12 @@
         <v>1.3361470789276</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Semnopithecus entellus</t>
-        </is>
+    <row r="164" spans="1:27">
+      <c r="A164" t="s">
+        <v>191</v>
+      </c>
+      <c r="B164" t="s">
+        <v>191</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -6815,16 +6735,12 @@
         <v>1.60688273588837</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Semnopithecus johnii</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Semnopithecus johnii</t>
-        </is>
+    <row r="165" spans="1:27">
+      <c r="A165" t="s">
+        <v>192</v>
+      </c>
+      <c r="B165" t="s">
+        <v>192</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -6845,16 +6761,12 @@
         <v>1.63848925695464</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Symphalangus syndactylus</t>
-        </is>
+    <row r="166" spans="1:27">
+      <c r="A166" t="s">
+        <v>193</v>
+      </c>
+      <c r="B166" t="s">
+        <v>193</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6899,16 +6811,12 @@
         <v>1.71048821835011</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Cephalopachus bancanus</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Cephalopachus bancanus</t>
-        </is>
+    <row r="167" spans="1:27">
+      <c r="A167" t="s">
+        <v>194</v>
+      </c>
+      <c r="B167" t="s">
+        <v>194</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -6959,16 +6867,12 @@
         <v>0.874336835397368</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Tarsius tarsier</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Tarsius tarsier</t>
-        </is>
+    <row r="168" spans="1:27">
+      <c r="A168" t="s">
+        <v>195</v>
+      </c>
+      <c r="B168" t="s">
+        <v>195</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -6983,16 +6887,12 @@
         <v>0.895974732359065</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Carlito syrichta</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Carlito syrichta</t>
-        </is>
+    <row r="169" spans="1:27">
+      <c r="A169" t="s">
+        <v>196</v>
+      </c>
+      <c r="B169" t="s">
+        <v>196</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -7043,16 +6943,12 @@
         <v>0.836324115706752</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Teilhardina belgica</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Teilhardina belgica</t>
-        </is>
+    <row r="170" spans="1:27">
+      <c r="A170" t="s">
+        <v>197</v>
+      </c>
+      <c r="B170" t="s">
+        <v>197</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -7076,16 +6972,12 @@
         <v>0.690196080028514</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>TheropithecusOmopithecus brumpti</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>TheropithecusOmopithecus brumpti</t>
-        </is>
+    <row r="171" spans="1:27">
+      <c r="A171" t="s">
+        <v>198</v>
+      </c>
+      <c r="B171" t="s">
+        <v>198</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -7148,16 +7040,12 @@
         <v>0.973127853599699</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Theropithecus gelada</t>
-        </is>
+    <row r="172" spans="1:27">
+      <c r="A172" t="s">
+        <v>199</v>
+      </c>
+      <c r="B172" t="s">
+        <v>199</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -7196,16 +7084,12 @@
         <v>1.6229217226423</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Tinimomys graybulliensis</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Tinimomys graybulliensis</t>
-        </is>
+    <row r="173" spans="1:27">
+      <c r="A173" t="s">
+        <v>200</v>
+      </c>
+      <c r="B173" t="s">
+        <v>200</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -7220,16 +7104,12 @@
         <v>0.667452952889954</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Trachypithecus auratus</t>
-        </is>
+    <row r="174" spans="1:27">
+      <c r="A174" t="s">
+        <v>201</v>
+      </c>
+      <c r="B174" t="s">
+        <v>201</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -7241,16 +7121,12 @@
         <v>1.5700757053216</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Trachypithecus obscurus</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Trachypithecus obscurus</t>
-        </is>
+    <row r="175" spans="1:27">
+      <c r="A175" t="s">
+        <v>202</v>
+      </c>
+      <c r="B175" t="s">
+        <v>202</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -7271,16 +7147,12 @@
         <v>1.54654266347813</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Trachypithecus phayrei</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Trachypithecus phayrei</t>
-        </is>
+    <row r="176" spans="1:27">
+      <c r="A176" t="s">
+        <v>203</v>
+      </c>
+      <c r="B176" t="s">
+        <v>203</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -7292,16 +7164,12 @@
         <v>1.57426282970703</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Trachypithecus pileatus</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Trachypithecus pileatus</t>
-        </is>
+    <row r="177" spans="1:24">
+      <c r="A177" t="s">
+        <v>204</v>
+      </c>
+      <c r="B177" t="s">
+        <v>204</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -7313,16 +7181,12 @@
         <v>1.60260252042026</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
+    <row r="178" spans="1:24">
+      <c r="A178" t="s">
+        <v>205</v>
+      </c>
+      <c r="B178" t="s">
+        <v>205</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -7349,16 +7213,12 @@
         <v>1.38728301948114</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Paralouatta varonai</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Paralouatta varonai</t>
-        </is>
+    <row r="179" spans="1:24">
+      <c r="A179" t="s">
+        <v>206</v>
+      </c>
+      <c r="B179" t="s">
+        <v>206</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -7651,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33CB7BB6-3DC2-4A0D-9B0D-D9963950E655}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F60FE169-05DC-42B6-95AC-6D518F204734}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65BF2CF0-A410-4E4F-AAE3-A1D2A2B6A847}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C4967B1-C62F-4B7A-8810-0AA7F6B40950}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19D4AADC-F950-42DF-A870-E85C0779808E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E23D707-8AFB-4DE2-8996-C49FD4D40BF5}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F60FE169-05DC-42B6-95AC-6D518F204734}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F50806BF-798F-46DF-9D79-44F54E4A8478}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C4967B1-C62F-4B7A-8810-0AA7F6B40950}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6532975-7372-460D-9049-437F4B8925E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E23D707-8AFB-4DE2-8996-C49FD4D40BF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF7CF8C3-2856-4E36-ACD3-DF32E09827ED}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F50806BF-798F-46DF-9D79-44F54E4A8478}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD0FE69D-7A08-4413-BF6F-058402716A8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6532975-7372-460D-9049-437F4B8925E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BDED094-54AE-43A2-A9AF-DD0AA2A184CA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF7CF8C3-2856-4E36-ACD3-DF32E09827ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB68D7A-223A-4B82-A510-6EBA9D56CCFF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7233,291 +7233,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD0FE69D-7A08-4413-BF6F-058402716A8A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BDED094-54AE-43A2-A9AF-DD0AA2A184CA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB68D7A-223A-4B82-A510-6EBA9D56CCFF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7233,4 +7233,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20B2EA4F-8BF1-468A-A36E-7B84E3FC9CA7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CCEC69F-3EF3-4D46-B7B4-C39E4EF41437}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03557A3E-476A-4D96-9500-FBC91DE5F9F3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7233,291 +7233,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20B2EA4F-8BF1-468A-A36E-7B84E3FC9CA7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CCEC69F-3EF3-4D46-B7B4-C39E4EF41437}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03557A3E-476A-4D96-9500-FBC91DE5F9F3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7233,4 +7233,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48167964-9131-4BA2-A1B0-753E366B580E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACE81D3F-BC7E-4847-BB9C-88211FE6F5D0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BFF90-DBAB-401F-8DA6-2F1FADD7C1E8}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48167964-9131-4BA2-A1B0-753E366B580E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C508A3C6-A3B3-4FA9-9E60-879714249701}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACE81D3F-BC7E-4847-BB9C-88211FE6F5D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB857D61-CC1A-4A79-8C52-1110336E9300}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BFF90-DBAB-401F-8DA6-2F1FADD7C1E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0B4E3D3-CFAC-45CA-812E-B0156BC9547F}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C508A3C6-A3B3-4FA9-9E60-879714249701}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DB24BB6-98DD-4800-9B02-5CDA3514AA1C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB857D61-CC1A-4A79-8C52-1110336E9300}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829F0A3A-8DC6-471A-829C-8BC75799D201}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0B4E3D3-CFAC-45CA-812E-B0156BC9547F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E625B4B6-C748-4F01-8E27-9FFA3E6EF4A4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DB24BB6-98DD-4800-9B02-5CDA3514AA1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9078577B-F5C3-465E-806D-61F9B82ACE7A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829F0A3A-8DC6-471A-829C-8BC75799D201}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB6B2F91-1E1B-49D2-86A6-6D209ABD8F41}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E625B4B6-C748-4F01-8E27-9FFA3E6EF4A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE9E64C1-5367-4E76-B9A8-72633D02587B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9078577B-F5C3-465E-806D-61F9B82ACE7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23727E73-494A-4184-B9EF-B4110D3BAB58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB6B2F91-1E1B-49D2-86A6-6D209ABD8F41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2978B070-4EE4-414B-B585-391CAD3FAD16}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE9E64C1-5367-4E76-B9A8-72633D02587B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87ADD6A0-36A0-460A-B2AA-1A7D19D36EA1}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7511,13 +7511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23727E73-494A-4184-B9EF-B4110D3BAB58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19530341-5A33-4216-8FCB-528787A98A0A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2978B070-4EE4-414B-B585-391CAD3FAD16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C24B10-9348-413C-B8B9-4E867AB31FAD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87ADD6A0-36A0-460A-B2AA-1A7D19D36EA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09ED7E87-C4CE-4256-ACC1-FBDC3DBF96F2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7233,291 +7233,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19530341-5A33-4216-8FCB-528787A98A0A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C24B10-9348-413C-B8B9-4E867AB31FAD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09ED7E87-C4CE-4256-ACC1-FBDC3DBF96F2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7233,4 +7233,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ECB97EA-2878-4CC4-A1FC-09194B15EA8F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01DE7DA2-D81D-4E33-B374-AD7AB3D01863}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88E8AEB-2BBE-4B6C-8558-18F2F7F4B810}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="205">
   <si>
     <t>species_sci</t>
   </si>
@@ -352,9 +352,6 @@
     <t>Indri indri</t>
   </si>
   <si>
-    <t>Lagothrix lagothricha</t>
-  </si>
-  <si>
     <t>Lagothrix lagotricha</t>
   </si>
   <si>
@@ -524,9 +521,6 @@
   </si>
   <si>
     <t>Plesiadapis tricuspidens</t>
-  </si>
-  <si>
-    <t>Pongo sp.</t>
   </si>
   <si>
     <t>Pongo abelii</t>
@@ -4121,7 +4115,7 @@
         <v>112</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4150,10 +4144,10 @@
     </row>
     <row r="88" spans="1:25">
       <c r="A88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -4188,10 +4182,10 @@
     </row>
     <row r="89" spans="1:25">
       <c r="A89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -4214,10 +4208,10 @@
     </row>
     <row r="90" spans="1:25">
       <c r="A90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4246,10 +4240,10 @@
     </row>
     <row r="91" spans="1:25">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4266,10 +4260,10 @@
     </row>
     <row r="92" spans="1:25">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4286,10 +4280,10 @@
     </row>
     <row r="93" spans="1:25">
       <c r="A93" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B93" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4318,10 +4312,10 @@
     </row>
     <row r="94" spans="1:25">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B94" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4350,10 +4344,10 @@
     </row>
     <row r="95" spans="1:25">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -4370,10 +4364,10 @@
     </row>
     <row r="96" spans="1:25">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4390,10 +4384,10 @@
     </row>
     <row r="97" spans="1:24">
       <c r="A97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -4458,10 +4452,10 @@
     </row>
     <row r="98" spans="1:24">
       <c r="A98" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -4499,10 +4493,10 @@
     </row>
     <row r="99" spans="1:24">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4543,10 +4537,10 @@
     </row>
     <row r="100" spans="1:24">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B100" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -4611,10 +4605,10 @@
     </row>
     <row r="101" spans="1:24">
       <c r="A101" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -4661,10 +4655,10 @@
     </row>
     <row r="102" spans="1:24">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -4711,10 +4705,10 @@
     </row>
     <row r="103" spans="1:24">
       <c r="A103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4728,10 +4722,10 @@
     </row>
     <row r="104" spans="1:24">
       <c r="A104" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -4763,10 +4757,10 @@
     </row>
     <row r="105" spans="1:24">
       <c r="A105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4792,10 +4786,10 @@
     </row>
     <row r="106" spans="1:24">
       <c r="A106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4827,10 +4821,10 @@
     </row>
     <row r="107" spans="1:24">
       <c r="A107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4853,10 +4847,10 @@
     </row>
     <row r="108" spans="1:24">
       <c r="A108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4876,10 +4870,10 @@
     </row>
     <row r="109" spans="1:24">
       <c r="A109" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B109" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -4926,10 +4920,10 @@
     </row>
     <row r="110" spans="1:24">
       <c r="A110" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B110" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -4976,10 +4970,10 @@
     </row>
     <row r="111" spans="1:24">
       <c r="A111" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -5002,10 +4996,10 @@
     </row>
     <row r="112" spans="1:24">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -5034,10 +5028,10 @@
     </row>
     <row r="113" spans="1:27">
       <c r="A113" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B113" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5048,10 +5042,10 @@
     </row>
     <row r="114" spans="1:27">
       <c r="A114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -5077,10 +5071,10 @@
     </row>
     <row r="115" spans="1:27">
       <c r="A115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5097,10 +5091,10 @@
     </row>
     <row r="116" spans="1:27">
       <c r="A116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5114,10 +5108,10 @@
     </row>
     <row r="117" spans="1:27">
       <c r="A117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -5143,10 +5137,10 @@
     </row>
     <row r="118" spans="1:27">
       <c r="A118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -5187,10 +5181,10 @@
     </row>
     <row r="119" spans="1:27">
       <c r="A119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5213,10 +5207,10 @@
     </row>
     <row r="120" spans="1:27">
       <c r="A120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -5275,10 +5269,10 @@
     </row>
     <row r="121" spans="1:27">
       <c r="A121" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5307,10 +5301,10 @@
     </row>
     <row r="122" spans="1:27">
       <c r="A122" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B122" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -5327,10 +5321,10 @@
     </row>
     <row r="123" spans="1:27">
       <c r="A123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -5359,10 +5353,10 @@
     </row>
     <row r="124" spans="1:27">
       <c r="A124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -5391,10 +5385,10 @@
     </row>
     <row r="125" spans="1:27">
       <c r="A125" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B125" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -5423,10 +5417,10 @@
     </row>
     <row r="126" spans="1:27">
       <c r="A126" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B126" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -5488,10 +5482,10 @@
     </row>
     <row r="127" spans="1:27">
       <c r="A127" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B127" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -5556,10 +5550,10 @@
     </row>
     <row r="128" spans="1:27">
       <c r="A128" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B128" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -5594,10 +5588,10 @@
     </row>
     <row r="129" spans="1:25">
       <c r="A129" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B129" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -5635,10 +5629,10 @@
     </row>
     <row r="130" spans="1:25">
       <c r="A130" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B130" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -5703,10 +5697,10 @@
     </row>
     <row r="131" spans="1:25">
       <c r="A131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B131" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5741,10 +5735,10 @@
     </row>
     <row r="132" spans="1:25">
       <c r="A132" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B132" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -5767,10 +5761,10 @@
     </row>
     <row r="133" spans="1:25">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -5796,10 +5790,10 @@
     </row>
     <row r="134" spans="1:25">
       <c r="A134" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B134" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -5819,10 +5813,10 @@
     </row>
     <row r="135" spans="1:25">
       <c r="A135" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B135" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -5839,10 +5833,10 @@
     </row>
     <row r="136" spans="1:25">
       <c r="A136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5853,10 +5847,10 @@
     </row>
     <row r="137" spans="1:25">
       <c r="A137" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B137" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -5879,10 +5873,10 @@
     </row>
     <row r="138" spans="1:25">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B138" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5905,10 +5899,10 @@
     </row>
     <row r="139" spans="1:25">
       <c r="A139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -5952,10 +5946,10 @@
     </row>
     <row r="140" spans="1:25">
       <c r="A140" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B140" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5999,10 +5993,10 @@
     </row>
     <row r="141" spans="1:25">
       <c r="A141" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B141" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -6013,10 +6007,10 @@
     </row>
     <row r="142" spans="1:25">
       <c r="A142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -6033,10 +6027,10 @@
     </row>
     <row r="143" spans="1:25">
       <c r="A143" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B143" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -6053,10 +6047,10 @@
     </row>
     <row r="144" spans="1:25">
       <c r="A144" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -6097,10 +6091,10 @@
     </row>
     <row r="145" spans="1:24">
       <c r="A145" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B145" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -6165,10 +6159,10 @@
     </row>
     <row r="146" spans="1:24">
       <c r="A146" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B146" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -6191,10 +6185,10 @@
     </row>
     <row r="147" spans="1:24">
       <c r="A147" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B147" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -6259,10 +6253,10 @@
     </row>
     <row r="148" spans="1:24">
       <c r="A148" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B148" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -6276,10 +6270,10 @@
     </row>
     <row r="149" spans="1:24">
       <c r="A149" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B149" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -6302,10 +6296,10 @@
     </row>
     <row r="150" spans="1:24">
       <c r="A150" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B150" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -6319,10 +6313,10 @@
     </row>
     <row r="151" spans="1:24">
       <c r="A151" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B151" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6345,10 +6339,10 @@
     </row>
     <row r="152" spans="1:24">
       <c r="A152" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B152" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6362,10 +6356,10 @@
     </row>
     <row r="153" spans="1:24">
       <c r="A153" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -6379,10 +6373,10 @@
     </row>
     <row r="154" spans="1:24">
       <c r="A154" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B154" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6411,10 +6405,10 @@
     </row>
     <row r="155" spans="1:24">
       <c r="A155" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B155" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6443,10 +6437,10 @@
     </row>
     <row r="156" spans="1:24">
       <c r="A156" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B156" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6475,10 +6469,10 @@
     </row>
     <row r="157" spans="1:24">
       <c r="A157" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B157" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -6501,10 +6495,10 @@
     </row>
     <row r="158" spans="1:24">
       <c r="A158" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B158" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6518,10 +6512,10 @@
     </row>
     <row r="159" spans="1:24">
       <c r="A159" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B159" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -6544,10 +6538,10 @@
     </row>
     <row r="160" spans="1:24">
       <c r="A160" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B160" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -6564,10 +6558,10 @@
     </row>
     <row r="161" spans="1:27">
       <c r="A161" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B161" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -6590,10 +6584,10 @@
     </row>
     <row r="162" spans="1:27">
       <c r="A162" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B162" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -6637,10 +6631,10 @@
     </row>
     <row r="163" spans="1:27">
       <c r="A163" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B163" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -6705,10 +6699,10 @@
     </row>
     <row r="164" spans="1:27">
       <c r="A164" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B164" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -6737,10 +6731,10 @@
     </row>
     <row r="165" spans="1:27">
       <c r="A165" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B165" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -6763,10 +6757,10 @@
     </row>
     <row r="166" spans="1:27">
       <c r="A166" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B166" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6813,10 +6807,10 @@
     </row>
     <row r="167" spans="1:27">
       <c r="A167" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B167" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -6869,10 +6863,10 @@
     </row>
     <row r="168" spans="1:27">
       <c r="A168" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B168" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -6889,10 +6883,10 @@
     </row>
     <row r="169" spans="1:27">
       <c r="A169" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B169" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -6945,10 +6939,10 @@
     </row>
     <row r="170" spans="1:27">
       <c r="A170" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B170" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -6974,10 +6968,10 @@
     </row>
     <row r="171" spans="1:27">
       <c r="A171" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B171" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -7042,10 +7036,10 @@
     </row>
     <row r="172" spans="1:27">
       <c r="A172" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B172" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -7086,10 +7080,10 @@
     </row>
     <row r="173" spans="1:27">
       <c r="A173" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B173" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -7106,10 +7100,10 @@
     </row>
     <row r="174" spans="1:27">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B174" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -7123,10 +7117,10 @@
     </row>
     <row r="175" spans="1:27">
       <c r="A175" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B175" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -7149,10 +7143,10 @@
     </row>
     <row r="176" spans="1:27">
       <c r="A176" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B176" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -7166,10 +7160,10 @@
     </row>
     <row r="177" spans="1:24">
       <c r="A177" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B177" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -7183,10 +7177,10 @@
     </row>
     <row r="178" spans="1:24">
       <c r="A178" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B178" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -7215,10 +7209,10 @@
     </row>
     <row r="179" spans="1:24">
       <c r="A179" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B179" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -7511,13 +7505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ECB97EA-2878-4CC4-A1FC-09194B15EA8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7B75B4C-816D-4BCF-A4CF-1F7864D657CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01DE7DA2-D81D-4E33-B374-AD7AB3D01863}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A6DFEF-D860-4A2B-A815-ECA184E40271}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F88E8AEB-2BBE-4B6C-8558-18F2F7F4B810}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AF08349-7589-4D8C-B8A8-10332028A50A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7505,13 +7505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7B75B4C-816D-4BCF-A4CF-1F7864D657CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF1FEE7A-D3CF-43A7-95C4-6F9E7D1B1333}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A6DFEF-D860-4A2B-A815-ECA184E40271}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A076B13-9DDF-4EF4-AB13-2B0A7D5955BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AF08349-7589-4D8C-B8A8-10332028A50A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{890F1695-E217-4DF2-A6A8-8FFFB65B847C}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7505,13 +7505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF1FEE7A-D3CF-43A7-95C4-6F9E7D1B1333}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A7C6026-C817-471A-8A8C-861018D712E0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A076B13-9DDF-4EF4-AB13-2B0A7D5955BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456DA301-7E7A-4ED0-90A3-7AE6450CD91F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{890F1695-E217-4DF2-A6A8-8FFFB65B847C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DD96565-7871-420E-83C5-42B8A980B0CF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7505,13 +7505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A7C6026-C817-471A-8A8C-861018D712E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EABF265-01B2-45C7-8F23-009E080D566F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456DA301-7E7A-4ED0-90A3-7AE6450CD91F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7FF6E54-064F-4624-BB17-E30A260CCC0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DD96565-7871-420E-83C5-42B8A980B0CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F333255-5BBE-4E6F-8024-1A696E7815F2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7505,13 +7505,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EABF265-01B2-45C7-8F23-009E080D566F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27953BBA-5713-47FE-8424-A17CA3C49EB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7FF6E54-064F-4624-BB17-E30A260CCC0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3791E46E-A179-4F9C-A3F5-C44ACA893A07}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F333255-5BBE-4E6F-8024-1A696E7815F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{969681F9-2D76-4D8B-A322-16AE6BBA6855}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7227,291 +7227,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27953BBA-5713-47FE-8424-A17CA3C49EB9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3791E46E-A179-4F9C-A3F5-C44ACA893A07}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{969681F9-2D76-4D8B-A322-16AE6BBA6855}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7227,4 +7227,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAA0712E-2643-4865-BBB8-BEF62C4796F5}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDF3DEA8-B012-4702-8B9C-390AD7EBF000}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2FDF462-10DB-4CAE-8717-C41ADB150D5B}"/>
 </file>